--- a/site/Lever-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/Lever-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,29 +617,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
+          <t>h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K0PGWJSDQBPT1BZ25EAQGNYR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
+          <t>h_01K0EPNYJEHDW4TQRTN6PXT579</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K0PGWJSDWRPH0DRX23RJ5DDJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K0EPNYJEHDW4TQRTN6PXT579</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Analytics Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K0EPNYJEHDW4TQRTN6PXT579</t>
+          <t>01K58GNXGG1YQW0AX744QCT7JV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K0EPNYJEHDW4TQRTN6PXT579</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#01K58GNXGG1YQW0AX744QCT7JV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01K58GNXGG1YQW0AX744QCT7JV</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#01K58GNXGG1YQW0AX744QCT7JV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Lever APIs Leveraged by this Integration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>h_01KNP2G0ZM8RRGXAM6WHBZZXY3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01KNP2G0ZM8RRGXAM6WHBZZXY3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lever APIs Leveraged by this Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,32 +781,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lever-apis-leveraged-by-this-integration</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#lever-apis-leveraged-by-this-integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Lever-UKG-Ready-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
